--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -538,14 +538,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30998</v>
+        <v>34992</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>53754</v>
+        <v>44246</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -555,27 +555,23 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -595,10 +591,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34992</v>
+        <v>34995</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>44246</v>
+        <v>53180</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -613,11 +609,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -666,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -715,7 +711,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -751,7 +747,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -766,7 +762,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -774,14 +770,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33995</v>
+        <v>34895</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>69400</v>
+        <v>59350</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -791,16 +787,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -815,42 +811,91 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>69400</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>34992</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>63289</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>18</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K9" t="n">
+        <v>19</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>35,492 → 34,992</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -859,6 +904,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4920,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5035,7 +5081,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5084,7 +5130,7 @@
         <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5133,7 +5179,7 @@
         <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5186,7 +5232,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5225,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5270,7 +5316,7 @@
         <v>55</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5319,7 +5365,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5368,7 +5414,7 @@
         <v>47</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5421,7 +5467,7 @@
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5470,7 +5516,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5519,7 +5565,7 @@
         <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5572,7 +5618,7 @@
         <v>22</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5621,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5666,7 +5712,7 @@
         <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5711,7 +5757,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5760,7 +5806,7 @@
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5813,7 +5859,7 @@
         <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5852,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5871,57 +5917,8 @@
       </c>
       <c r="M19" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>48677</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>18</v>
-      </c>
-      <c r="I20" t="n">
-        <v>21</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M20"/>
+  <autoFilter ref="A1:M19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5941,7 +5938,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>55</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>47</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>22</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -538,14 +538,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>34992</v>
+        <v>34995</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>44246</v>
+        <v>60487</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -560,11 +560,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -591,10 +591,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34995</v>
+        <v>34992</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>53180</v>
+        <v>44246</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -609,11 +609,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -628,11 +628,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>67680</v>
+        <v>53180</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -658,11 +658,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52500</v>
+        <v>67680</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -707,11 +707,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -726,28 +726,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2023</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>31998</v>
+        <v>33495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>56361</v>
+        <v>52500</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -762,41 +775,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="n">
-        <v>34895</v>
+        <v>31998</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>59350</v>
+        <v>56361</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -819,14 +819,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>33995</v>
+        <v>34895</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>69400</v>
+        <v>59350</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
@@ -836,16 +836,16 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -860,42 +860,91 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2023</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>69400</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>34992</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>63289</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="K10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>35,492 → 34,992</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -905,6 +954,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5081,7 +5131,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5130,7 +5180,7 @@
         <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5179,7 +5229,7 @@
         <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5232,7 +5282,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5271,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5316,7 +5366,7 @@
         <v>55</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5365,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5414,7 +5464,7 @@
         <v>47</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5467,7 +5517,7 @@
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5516,7 +5566,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5565,7 +5615,7 @@
         <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5618,7 +5668,7 @@
         <v>22</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5667,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5712,7 +5762,7 @@
         <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5757,7 +5807,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5806,7 +5856,7 @@
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5859,7 +5909,7 @@
         <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5898,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>55</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>47</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>22</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5131,7 +5131,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>55</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>47</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>22</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5826,149 +5826,8 @@
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>33650</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>9</v>
-      </c>
-      <c r="I17" t="n">
-        <v>21</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>68226</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>21</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Toyotavictoriaville</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>21</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:M16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5985,9 +5844,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>55</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>47</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>22</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -943,8 +943,84 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>61005</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Toyotavictoriaville</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Toyotavictoriaville</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -955,6 +1031,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5016,7 +5094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5131,7 +5209,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5180,7 +5258,7 @@
         <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5229,7 +5307,7 @@
         <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5282,7 +5360,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5321,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5366,7 +5444,7 @@
         <v>55</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5415,7 +5493,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5464,7 +5542,7 @@
         <v>47</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5517,7 +5595,7 @@
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5566,7 +5644,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5615,7 +5693,7 @@
         <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5668,7 +5746,7 @@
         <v>22</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5717,7 +5795,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5736,98 +5814,8 @@
       </c>
       <c r="M14" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" s="2" t="n">
-        <v>32999</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>55369</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>19</v>
-      </c>
-      <c r="I15" t="n">
-        <v>21</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" s="2" t="n">
-        <v>33998</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>56937</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>21</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5842,8 +5830,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67680</v>
+        <v>55829</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -707,11 +707,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52500</v>
+        <v>67680</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -756,11 +756,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -775,28 +775,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="n">
-        <v>31998</v>
+        <v>33495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>56361</v>
+        <v>52500</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -845,7 +858,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -894,7 +907,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -930,7 +943,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -943,84 +956,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>61005</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Toyotavictoriaville</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Toyotavictoriaville</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1031,8 +968,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5094,7 +5029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5182,43 +5117,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>32495</v>
+        <v>31998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>67680</v>
+        <v>56361</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5231,43 +5162,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>32495</v>
+          <t>GT S-AWC</t>
+        </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>27647</v>
+        <v>61005</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5280,43 +5208,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>26500</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>37866</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5324,16 +5242,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200 → 26,500</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5341,30 +5255,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33907</v>
+        <v>32495</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>60831</v>
+        <v>67680</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5382,28 +5296,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>32495</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>27647</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5421,39 +5345,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>34998</v>
+        <v>26500</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>67017</v>
+        <v>37866</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5461,27 +5389,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200 → 26,500</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>34995</v>
+        <v>33907</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60062</v>
+        <v>60831</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5490,19 +5422,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5515,43 +5447,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>31500</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>39577</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5559,52 +5481,44 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2024</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>67531</v>
+        <v>67017</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5617,7 +5531,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5625,14 +5539,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>35299</v>
+        <v>34995</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>53475</v>
+        <v>60062</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5641,19 +5555,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
         <v>12</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5666,7 +5580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5674,14 +5588,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>33897</v>
+        <v>31500</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>32954</v>
+        <v>39577</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5690,19 +5604,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5712,14 +5626,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>34,997 → 33,897</t>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5727,14 +5641,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
         <v>34995</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>60062</v>
+        <v>67531</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5743,19 +5657,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5763,59 +5677,210 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>32488</v>
+        <v>35299</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>63212</v>
+        <v>53475</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>33897</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>32954</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>23</v>
+      </c>
+      <c r="I15" t="n">
+        <v>17</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>34,997 → 33,897</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>34995</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>60062</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>22</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" s="2" t="n">
+        <v>32488</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>63212</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Repentigny Mitsubishi</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="n">
-        <v>18</v>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
+  <autoFilter ref="A1:M17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5830,6 +5895,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>29</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>27</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>23</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>55</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>23</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>22</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5140,7 +5140,7 @@
         <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>29</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>27</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>23</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>55</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>23</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5781,106 +5781,8 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>60062</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>22</v>
-      </c>
-      <c r="I16" t="n">
-        <v>21</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" s="2" t="n">
-        <v>32488</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>63212</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>21</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:M15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5896,8 +5798,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>29</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>27</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>23</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>55</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>23</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -591,10 +591,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34992</v>
+        <v>34995</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>44246</v>
+        <v>53180</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -609,11 +609,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>34995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>53180</v>
+        <v>55829</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34995</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55829</v>
+        <v>67680</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -707,11 +707,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67680</v>
+        <v>52500</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -756,11 +756,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -775,22 +775,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33495</v>
+        <v>34988</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>52500</v>
+        <v>61258</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5117,39 +5117,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5162,35 +5166,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -5208,13 +5211,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2024</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
@@ -5225,7 +5235,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5247,43 +5257,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>67680</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5311,23 +5311,23 @@
         <v>32495</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>27647</v>
+        <v>67680</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5345,7 +5345,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5353,14 +5353,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>26500</v>
+        <v>32495</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37866</v>
+        <v>27647</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5369,14 +5369,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5389,11 +5389,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200 → 26,500</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5410,10 +5406,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>33907</v>
+        <v>26500</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60831</v>
+        <v>37866</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5422,14 +5418,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5442,33 +5438,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200 → 26,500</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>33907</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>60831</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5486,39 +5496,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>67017</v>
-      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5531,38 +5535,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2024</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>60062</v>
+        <v>67017</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5580,22 +5580,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>31500</v>
+        <v>34995</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>39577</v>
+        <v>60062</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5604,19 +5604,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>16</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5624,31 +5624,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34995</v>
+        <v>31500</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>67531</v>
+        <v>39577</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5657,14 +5653,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5677,12 +5673,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5690,14 +5690,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>35299</v>
+        <v>34995</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>53475</v>
+        <v>67531</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5706,19 +5706,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
         <v>17</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5731,22 +5731,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>33897</v>
+        <v>35299</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>32954</v>
+        <v>53475</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5755,34 +5755,83 @@
         </is>
       </c>
       <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>18</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>33897</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>32954</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>23</v>
       </c>
-      <c r="I15" t="n">
-        <v>20</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="I16" t="n">
+        <v>21</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>34,997 → 33,897</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M15"/>
+  <autoFilter ref="A1:M16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5798,6 +5847,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -775,22 +775,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34988</v>
+        <v>32495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>61258</v>
+        <v>69400</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -809,14 +809,18 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>33,995 → 32,495</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -824,22 +828,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34895</v>
+        <v>34988</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>59350</v>
+        <v>61258</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
@@ -849,16 +853,16 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, CarPlay, Android Auto</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -873,41 +877,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2023</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="n">
-        <v>33995</v>
+        <v>34895</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>69400</v>
+        <v>59350</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -943,7 +934,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -5117,43 +5108,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5166,39 +5157,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5211,35 +5206,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5257,13 +5251,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2024</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
@@ -5274,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5296,43 +5297,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>67680</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5360,23 +5351,23 @@
         <v>32495</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>27647</v>
+        <v>67680</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5394,7 +5385,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5402,14 +5393,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>26500</v>
+        <v>32495</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>37866</v>
+        <v>27647</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5418,14 +5409,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5438,11 +5429,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200 → 26,500</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5459,10 +5446,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>33907</v>
+        <v>26500</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>60831</v>
+        <v>37866</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5471,14 +5458,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5491,33 +5478,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200 → 26,500</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>33907</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>60831</v>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5535,39 +5536,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>67017</v>
-      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5580,38 +5575,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2024</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>60062</v>
+        <v>67017</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5629,22 +5620,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>31500</v>
+        <v>34995</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>39577</v>
+        <v>60062</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5653,19 +5644,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
         <v>17</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5673,31 +5664,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34995</v>
+        <v>31500</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>67531</v>
+        <v>39577</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5706,14 +5693,14 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5726,12 +5713,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5739,14 +5730,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>35299</v>
+        <v>34995</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>53475</v>
+        <v>67531</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5755,19 +5746,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
         <v>18</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5780,22 +5771,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>33897</v>
+        <v>35299</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32954</v>
+        <v>53475</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5804,19 +5795,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5824,11 +5815,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>34,997 → 33,897</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M16"/>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34995</v>
+        <v>34994</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>55829</v>
+        <v>54959</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67680</v>
+        <v>55829</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -707,11 +707,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52500</v>
+        <v>67680</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -756,11 +756,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -809,18 +809,14 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -828,22 +824,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34988</v>
+        <v>32495</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>61258</v>
+        <v>69400</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
@@ -853,7 +849,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -862,14 +858,18 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>33,995 → 32,495</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -877,28 +877,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34895</v>
+        <v>34988</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>59350</v>
+        <v>61258</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sunroof, CarPlay, Android Auto</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -913,42 +926,87 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2023</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="n">
+        <v>34895</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>59350</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>34992</v>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>63289</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>32</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -959,6 +1017,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5020,7 +5079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5108,43 +5167,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5152,48 +5207,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5206,39 +5261,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5251,35 +5310,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5297,13 +5355,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2024</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
@@ -5314,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5336,43 +5401,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>67680</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5400,23 +5455,23 @@
         <v>32495</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>27647</v>
+        <v>67680</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5434,7 +5489,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5442,14 +5497,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>26500</v>
+        <v>32495</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>37866</v>
+        <v>27647</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5458,14 +5513,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5478,11 +5533,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200 → 26,500</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5499,10 +5550,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>33907</v>
+        <v>26500</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>60831</v>
+        <v>37866</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5511,14 +5562,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5531,33 +5582,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200 → 26,500</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>33907</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>60831</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5575,39 +5640,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>67017</v>
-      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5620,38 +5679,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2024</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>60062</v>
+        <v>67017</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5669,22 +5724,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>31500</v>
+        <v>34995</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>39577</v>
+        <v>60062</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5693,19 +5748,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
         <v>18</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5713,31 +5768,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34995</v>
+        <v>31500</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>67531</v>
+        <v>39577</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5746,14 +5797,14 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5766,12 +5817,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5779,14 +5834,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>35299</v>
+        <v>34995</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>53475</v>
+        <v>67531</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5795,30 +5850,79 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
         <v>19</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>35299</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>53475</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5835,6 +5939,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34994</v>
+        <v>34983</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>54959</v>
@@ -662,14 +662,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>34,994 → 34,983</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -711,7 +715,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -726,22 +730,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32495</v>
+        <v>34990</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67680</v>
+        <v>59312</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -756,11 +760,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -787,10 +791,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>52500</v>
+        <v>67680</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -805,11 +809,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -836,10 +840,10 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
@@ -858,18 +862,14 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -877,22 +877,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34988</v>
+        <v>32495</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>61258</v>
+        <v>69400</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -911,14 +911,18 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>33,995 → 32,495</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -926,22 +930,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34895</v>
+        <v>34988</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>59350</v>
+        <v>61258</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -951,16 +955,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, CarPlay, Android Auto</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -996,7 +1000,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -5079,7 +5083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5167,39 +5171,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>63289</v>
+        <v>59350</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5207,11 +5215,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5224,80 +5228,80 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5310,39 +5314,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5355,35 +5363,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5401,13 +5408,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2024</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
@@ -5418,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5440,43 +5454,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>67680</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5504,23 +5508,23 @@
         <v>32495</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>27647</v>
+        <v>67680</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5538,7 +5542,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5546,14 +5550,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>26500</v>
+        <v>32495</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>37866</v>
+        <v>27647</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5562,14 +5566,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5582,11 +5586,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200 → 26,500</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>33907</v>
+        <v>26500</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>60831</v>
+        <v>37866</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5615,14 +5615,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5635,33 +5635,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200 → 26,500</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>33907</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>60831</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5679,39 +5693,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>67017</v>
-      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5724,38 +5732,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2024</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>60062</v>
+        <v>67017</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5773,22 +5777,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>31500</v>
+        <v>34995</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>39577</v>
+        <v>60062</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5797,19 +5801,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
         <v>19</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5817,31 +5821,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>34995</v>
+        <v>31500</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>67531</v>
+        <v>39577</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5850,14 +5850,14 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5870,12 +5870,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5883,14 +5887,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>35299</v>
+        <v>34995</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>53475</v>
+        <v>67531</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -5899,30 +5903,79 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
         <v>20</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>35299</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>53475</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>21</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:M18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5940,6 +5993,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -538,14 +538,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>60487</v>
+        <v>53180</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,14 +564,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -579,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -587,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>34995</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>53180</v>
+        <v>60487</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -613,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -662,7 +666,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -715,7 +719,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -730,7 +734,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -738,14 +742,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34990</v>
+        <v>35494</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>59312</v>
+        <v>47574</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -813,7 +817,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -862,7 +866,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -911,7 +915,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -964,7 +968,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1000,7 +1004,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -5171,22 +5175,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34895</v>
+        <v>34990</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>59350</v>
+        <v>59312</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5195,19 +5199,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5220,39 +5224,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>63289</v>
+        <v>59350</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5260,11 +5268,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5277,80 +5281,80 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5363,39 +5367,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5408,35 +5416,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5454,13 +5461,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2024</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
@@ -5471,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5493,43 +5507,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>67680</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5557,23 +5561,23 @@
         <v>32495</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>27647</v>
+        <v>67680</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5591,7 +5595,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5599,14 +5603,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>26500</v>
+        <v>32495</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>37866</v>
+        <v>27647</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5615,14 +5619,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5635,11 +5639,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200 → 26,500</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>33907</v>
+        <v>26500</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>60831</v>
+        <v>37866</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5668,14 +5668,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5688,33 +5688,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200 → 26,500</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>33907</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>60831</v>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5732,39 +5746,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>67017</v>
-      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5777,38 +5785,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2024</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>60062</v>
+        <v>67017</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5826,22 +5830,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>31500</v>
+        <v>34995</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39577</v>
+        <v>60062</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5850,19 +5854,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
         <v>20</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5870,31 +5874,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>34995</v>
+        <v>31500</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>67531</v>
+        <v>39577</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -5903,14 +5903,14 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5923,12 +5923,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5936,14 +5940,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>35299</v>
+        <v>34995</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>53475</v>
+        <v>67531</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -5952,19 +5956,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
         <v>21</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33995</v>
+        <v>32893</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>53180</v>
+        <v>54959</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>34,995 → 33,995</t>
+          <t>34,994 → 34,983 → 32,893</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>60487</v>
+        <v>53180</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -617,14 +617,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,7 +636,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +644,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34983</v>
+        <v>34995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>54959</v>
+        <v>60487</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -666,18 +670,14 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>67680</v>
+        <v>52500</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -813,11 +813,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>52500</v>
+        <v>69400</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
@@ -866,14 +866,18 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>33,995 → 32,495</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -881,22 +885,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>32495</v>
+        <v>34988</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>69400</v>
+        <v>61258</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -906,7 +910,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof, CarPlay, Android Auto</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -915,18 +919,14 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -934,41 +934,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34988</v>
+        <v>34992</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>61258</v>
+        <v>57600</v>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Sunroof, CarPlay, Android Auto</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -977,44 +964,8 @@
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>57600</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1025,7 +976,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5087,7 +5037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5175,43 +5125,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>59312</v>
+        <v>67680</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5224,22 +5174,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34895</v>
+        <v>34990</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>59350</v>
+        <v>59312</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5248,19 +5198,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5273,39 +5223,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>63289</v>
+        <v>59350</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5313,11 +5267,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5330,80 +5280,80 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5416,39 +5366,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5461,35 +5415,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5507,13 +5460,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2024</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
@@ -5524,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5546,43 +5506,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>67680</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5610,23 +5560,23 @@
         <v>32495</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>27647</v>
+        <v>67680</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5644,7 +5594,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5652,14 +5602,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>26500</v>
+        <v>32495</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>37866</v>
+        <v>27647</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5668,14 +5618,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5688,11 +5638,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200 → 26,500</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5709,10 +5655,10 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>33907</v>
+        <v>26500</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>60831</v>
+        <v>37866</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5721,14 +5667,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5741,33 +5687,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200 → 26,500</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>33907</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>60831</v>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5785,39 +5745,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>67017</v>
-      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5830,38 +5784,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2024</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>60062</v>
+        <v>67017</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5879,22 +5829,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>31500</v>
+        <v>34995</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>39577</v>
+        <v>60062</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -5903,19 +5853,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
         <v>21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5923,63 +5873,10 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>67531</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>7</v>
-      </c>
-      <c r="I18" t="n">
-        <v>21</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
+  <autoFilter ref="A1:M17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5997,7 +5894,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5152,7 +5152,7 @@
         <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>32</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>29</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>27</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5781,102 +5781,8 @@
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>67017</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" t="n">
-        <v>21</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>60062</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>6</v>
-      </c>
-      <c r="I17" t="n">
-        <v>21</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:M15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5892,8 +5798,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$15</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -644,14 +644,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>60487</v>
+        <v>55829</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -670,14 +670,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -685,7 +689,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -693,14 +697,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>34995</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55829</v>
+        <v>60487</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -719,7 +723,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -768,7 +772,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -817,7 +821,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -866,7 +870,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -919,7 +923,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -934,38 +938,74 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34992</v>
+        <v>35490</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>57600</v>
+        <v>49731</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
+          <t>Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>34992</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -976,6 +1016,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5152,7 +5193,7 @@
         <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5201,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5250,7 +5291,7 @@
         <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5295,7 +5336,7 @@
         <v>32</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5344,7 +5385,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5393,7 +5434,7 @@
         <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5438,7 +5479,7 @@
         <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5484,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5523,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5572,7 +5613,7 @@
         <v>29</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5621,7 +5662,7 @@
         <v>27</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5670,7 +5711,7 @@
         <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5723,7 +5764,7 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5762,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -636,52 +636,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2024</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="n">
-        <v>33995</v>
+        <v>32995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>55829</v>
+        <v>50154</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>St Hyacinthe Mitsubishi, Otogo.ca</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -689,7 +672,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -697,14 +680,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>60487</v>
+        <v>55829</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -723,14 +706,18 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -738,7 +725,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -746,14 +733,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35494</v>
+        <v>34995</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>47574</v>
+        <v>60487</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -772,7 +759,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -787,11 +774,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -799,10 +786,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33495</v>
+        <v>35494</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>52500</v>
+        <v>47574</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -821,7 +808,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -836,22 +823,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>32495</v>
+        <v>35490</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>69400</v>
+        <v>49731</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
@@ -866,22 +853,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -889,22 +872,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34988</v>
+        <v>33495</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>61258</v>
+        <v>52500</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -914,7 +897,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -923,7 +906,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -938,35 +921,52 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>35490</v>
+        <v>32495</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>49731</v>
+        <v>69400</v>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>33,995 → 32,495</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -974,38 +974,87 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>34988</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>61258</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sunroof, CarPlay, Android Auto</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>2023</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E12" s="2" t="n">
         <v>34992</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>57600</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1017,6 +1066,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5078,7 +5128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5166,43 +5216,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>32495</v>
+        <v>35490</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>67680</v>
+        <v>49731</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5215,43 +5261,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>59312</v>
+        <v>67680</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5264,22 +5310,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34895</v>
+        <v>34990</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>59350</v>
+        <v>59312</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5288,19 +5334,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5313,39 +5359,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>63289</v>
+        <v>59350</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5353,11 +5403,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5370,80 +5416,80 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5456,39 +5502,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5501,35 +5551,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5547,13 +5596,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2024</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
@@ -5564,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5586,43 +5642,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>67680</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5650,23 +5696,23 @@
         <v>32495</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>27647</v>
+        <v>67680</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5684,7 +5730,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5692,14 +5738,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>26500</v>
+        <v>32495</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37866</v>
+        <v>27647</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5708,14 +5754,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5728,11 +5774,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200 → 26,500</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5749,10 +5791,10 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>33907</v>
+        <v>26500</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>60831</v>
+        <v>37866</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5761,14 +5803,14 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5781,49 +5823,102 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200 → 26,500</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>33907</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>60831</v>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>21</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>Lefebvre Toyota</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="n">
-        <v>20</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="I16" t="n">
+        <v>21</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M15"/>
+  <autoFilter ref="A1:M16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5839,6 +5934,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -636,35 +636,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2024</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="n">
-        <v>32995</v>
+        <v>33995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>50154</v>
+        <v>55829</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -672,7 +689,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -680,14 +697,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55829</v>
+        <v>60487</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -706,18 +723,14 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -725,7 +738,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -733,14 +746,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34995</v>
+        <v>35494</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>60487</v>
+        <v>47574</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -759,7 +772,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -774,7 +787,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -782,14 +795,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35494</v>
+        <v>35490</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>47574</v>
+        <v>49731</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -804,11 +817,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -823,22 +836,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>35490</v>
+        <v>33495</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>49731</v>
+        <v>52500</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
@@ -853,11 +866,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -884,10 +897,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>52500</v>
+        <v>69400</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -906,14 +919,18 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>33,995 → 32,495</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -921,22 +938,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>32495</v>
+        <v>34988</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>69400</v>
+        <v>61258</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -946,7 +963,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof, CarPlay, Android Auto</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -955,18 +972,14 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -974,22 +987,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34988</v>
+        <v>35499</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>61258</v>
+        <v>48779</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -999,7 +1012,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1008,7 +1021,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1044,7 +1057,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -5128,7 +5141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5224,15 +5237,15 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>35490</v>
+        <v>32995</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>49731</v>
+        <v>50154</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>St Hyacinthe Mitsubishi, Otogo.ca</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -5243,12 +5256,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5261,43 +5274,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>32495</v>
+        <v>35490</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>67680</v>
+        <v>49731</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5310,43 +5319,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>59312</v>
+        <v>67680</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5359,22 +5368,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34895</v>
+        <v>34990</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>59350</v>
+        <v>59312</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5383,19 +5392,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5408,39 +5417,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>63289</v>
+        <v>59350</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
         <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5448,11 +5461,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5465,80 +5474,80 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5551,39 +5560,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5596,35 +5609,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5642,13 +5654,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2024</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
@@ -5659,7 +5678,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5681,43 +5700,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>67680</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5727,198 +5736,8 @@
       </c>
       <c r="M12" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>27647</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>27</v>
-      </c>
-      <c r="I13" t="n">
-        <v>21</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>26500</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>37866</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>23</v>
-      </c>
-      <c r="I14" t="n">
-        <v>21</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200 → 26,500</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>33907</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>60831</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" t="n">
-        <v>21</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>21</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5931,10 +5750,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,52 +530,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>2024</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="n">
-        <v>32893</v>
+        <v>32995</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>54959</v>
+        <v>50154</v>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983 → 32,893</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -583,52 +566,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33995</v>
+        <v>30995</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>53180</v>
+        <v>63212</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -636,52 +602,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2024</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="n">
-        <v>33995</v>
+        <v>34492</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>55829</v>
+        <v>43909</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -689,41 +638,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2024</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="n">
-        <v>34995</v>
+        <v>35490</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>60487</v>
+        <v>49731</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -738,41 +674,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35494</v>
+        <v>34992</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>47574</v>
+        <v>57600</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -781,305 +704,14 @@
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>35490</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>49731</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>33495</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>52500</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>50</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>69400</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>26</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>34988</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>61258</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Sunroof, CarPlay, Android Auto</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>35499</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>48779</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>57600</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5141,7 +4773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5229,39 +4861,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
-        <v>32995</v>
+        <v>33495</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>50154</v>
+        <v>52500</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5274,39 +4910,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>35490</v>
+        <v>32495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>49731</v>
+        <v>69400</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H3" t="n">
+        <v>26</v>
+      </c>
+      <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5314,16 +4954,20 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>33,995 → 32,495</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5331,31 +4975,31 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32495</v>
+        <v>33995</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>67680</v>
+        <v>53180</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5363,12 +5007,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5376,35 +5024,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34990</v>
+        <v>34995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>59312</v>
+        <v>60487</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H5" t="n">
+        <v>19</v>
+      </c>
+      <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5417,43 +5065,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34895</v>
+        <v>33995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>59350</v>
+        <v>55829</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5461,44 +5109,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>34992</v>
+        <v>34988</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>63289</v>
+        <v>61258</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5506,48 +5162,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>34895</v>
+        <v>32893</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>59350</v>
+        <v>54959</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="n">
-        <v>7</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5555,7 +5211,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>34,994 → 34,983 → 32,893</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5572,31 +5232,31 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34992</v>
+        <v>35494</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>44246</v>
+        <v>47574</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5609,39 +5269,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
-        <v>31998</v>
+        <v>35490</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>56361</v>
+        <v>49731</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5654,40 +5318,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
-        </is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>35499</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>61005</v>
+        <v>48779</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5700,44 +5367,425 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>32495</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>67680</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>59312</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>34895</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>59350</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>34992</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>63289</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>32</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" s="2" t="n">
+        <v>34895</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>59350</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>34992</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>44246</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>18</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" s="2" t="n">
+        <v>31998</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>56361</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>61005</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Toyotavictoriaville</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="I19" t="n">
+        <v>15</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Toyotavictoriaville</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5750,6 +5798,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34492</v>
+        <v>34392</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>43909</v>
@@ -623,14 +623,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>34,492 → 34,392</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -659,7 +663,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -695,7 +699,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -4888,7 +4892,7 @@
         <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4937,7 +4941,7 @@
         <v>26</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4990,7 +4994,7 @@
         <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5043,7 +5047,7 @@
         <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5092,7 +5096,7 @@
         <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5145,7 +5149,7 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5194,7 +5198,7 @@
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5247,7 +5251,7 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5296,7 +5300,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5345,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5394,7 +5398,7 @@
         <v>50</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5443,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5492,7 +5496,7 @@
         <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5537,7 +5541,7 @@
         <v>32</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5586,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5635,7 +5639,7 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5680,7 +5684,7 @@
         <v>20</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5726,7 +5730,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5765,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -566,35 +566,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30995</v>
+        <v>34392</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>63212</v>
+        <v>43909</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>34,492 → 34,392</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -609,32 +613,28 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34392</v>
+        <v>35490</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>43909</v>
+        <v>49731</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>34,492 → 34,392</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -642,28 +642,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35490</v>
+        <v>34992</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>49731</v>
+        <v>57600</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -672,50 +672,13 @@
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>57600</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4777,7 +4740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4865,43 +4828,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>33495</v>
+        <v>30995</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>52500</v>
+        <v>63212</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -4926,10 +4885,10 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -4938,14 +4897,14 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4958,20 +4917,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4979,10 +4934,10 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>33995</v>
+        <v>32495</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>53180</v>
+        <v>69400</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -4991,14 +4946,14 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5013,14 +4968,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>34,995 → 33,995</t>
+          <t>33,995 → 32,495</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5028,14 +4983,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>60487</v>
+        <v>53180</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5044,14 +4999,14 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5064,12 +5019,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5077,14 +5036,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>55829</v>
+        <v>60487</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5093,14 +5052,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5113,16 +5072,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5130,14 +5085,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34988</v>
+        <v>33995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>61258</v>
+        <v>55829</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5146,14 +5101,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5166,12 +5121,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5179,14 +5138,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32893</v>
+        <v>34988</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>54959</v>
+        <v>61258</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5195,14 +5154,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5215,11 +5174,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983 → 32,893</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5236,10 +5191,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>35494</v>
+        <v>32893</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>47574</v>
+        <v>54959</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5248,14 +5203,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5268,12 +5223,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>34,994 → 34,983 → 32,893</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5281,30 +5240,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>35490</v>
+        <v>35494</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>49731</v>
+        <v>47574</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5322,38 +5281,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>35499</v>
+        <v>35490</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>48779</v>
+        <v>49731</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5371,7 +5330,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5379,35 +5338,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>32495</v>
+        <v>35499</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>67680</v>
+        <v>48779</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5420,43 +5379,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>59312</v>
+        <v>67680</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I13" t="n">
         <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5469,22 +5428,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34895</v>
+        <v>34990</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>59350</v>
+        <v>59312</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5493,19 +5452,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5518,39 +5477,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>63289</v>
+        <v>59350</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
         <v>9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5558,11 +5521,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5575,80 +5534,80 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5661,39 +5620,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5706,35 +5669,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5752,13 +5714,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2024</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
@@ -5769,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5788,8 +5757,47 @@
       </c>
       <c r="M20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Toyotavictoriaville</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>17</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M20"/>
+  <autoFilter ref="A1:M21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5810,6 +5818,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -606,28 +606,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>35490</v>
+        <v>34990</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>49731</v>
+        <v>60688</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -642,43 +655,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34992</v>
+        <v>35490</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>57600</v>
+        <v>49731</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
+          <t>Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>34992</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M5"/>
+  <autoFilter ref="A1:M6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4851,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4900,7 +4950,7 @@
         <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4949,7 +4999,7 @@
         <v>26</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5002,7 +5052,7 @@
         <v>21</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5055,7 +5105,7 @@
         <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5104,7 +5154,7 @@
         <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5157,7 +5207,7 @@
         <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5206,7 +5256,7 @@
         <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5259,7 +5309,7 @@
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5308,7 +5358,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5357,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5406,7 +5456,7 @@
         <v>50</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5455,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5504,7 +5554,7 @@
         <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5549,7 +5599,7 @@
         <v>32</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5598,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5647,7 +5697,7 @@
         <v>18</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5692,7 +5742,7 @@
         <v>20</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5738,7 +5788,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5777,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -655,28 +655,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35490</v>
+        <v>34992</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>49731</v>
+        <v>57600</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -685,50 +685,13 @@
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>57600</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>11</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4790,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4878,18 +4841,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>30995</v>
+        <v>35490</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>63212</v>
+        <v>49731</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -4898,19 +4861,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -4923,43 +4886,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>33495</v>
+        <v>30995</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>52500</v>
+        <v>63212</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -4984,10 +4943,10 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -4996,14 +4955,14 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5016,20 +4975,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5037,10 +4992,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33995</v>
+        <v>32495</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>53180</v>
+        <v>69400</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5049,14 +5004,14 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5071,14 +5026,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>34,995 → 33,995</t>
+          <t>33,995 → 32,495</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5086,14 +5041,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>60487</v>
+        <v>53180</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5102,14 +5057,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5122,12 +5077,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5135,14 +5094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>55829</v>
+        <v>60487</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5151,14 +5110,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5171,16 +5130,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5188,14 +5143,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>34988</v>
+        <v>33995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>61258</v>
+        <v>55829</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5204,14 +5159,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5224,12 +5179,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5237,14 +5196,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>32893</v>
+        <v>34988</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>54959</v>
+        <v>61258</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5253,14 +5212,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5273,11 +5232,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983 → 32,893</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5294,10 +5249,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>35494</v>
+        <v>32893</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>47574</v>
+        <v>54959</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5306,14 +5261,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5326,12 +5281,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>34,994 → 34,983 → 32,893</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5339,30 +5298,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>35490</v>
+        <v>35494</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>49731</v>
+        <v>47574</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5380,38 +5339,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>35499</v>
+        <v>35490</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>48779</v>
+        <v>49731</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5429,7 +5388,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5437,35 +5396,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>32495</v>
+        <v>35499</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>67680</v>
+        <v>48779</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5478,43 +5437,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>59312</v>
+        <v>67680</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I14" t="n">
         <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5527,22 +5486,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34895</v>
+        <v>34990</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>59350</v>
+        <v>59312</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5551,19 +5510,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>10</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5576,39 +5535,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2023</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>63289</v>
+        <v>59350</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I16" t="n">
         <v>11</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5616,11 +5579,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5633,80 +5592,80 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5719,39 +5678,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5764,35 +5727,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5810,13 +5772,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2024</v>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
@@ -5827,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5846,8 +5815,47 @@
       </c>
       <c r="M21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Toyotavictoriaville</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>19</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M21"/>
+  <autoFilter ref="A1:M22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5869,6 +5877,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,28 +530,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32995</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>50154</v>
+        <v>33488</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,21 +570,21 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34392</v>
+        <v>32500</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>43909</v>
+        <v>50154</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -596,7 +593,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>34,492 → 34,392</t>
+          <t>32,995 → 32,500</t>
         </is>
       </c>
     </row>
@@ -606,48 +603,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34990</v>
+        <v>34392</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>60688</v>
+        <v>43909</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>34,492 → 34,392</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -655,43 +643,93 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2023</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>60688</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>34992</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>57600</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="K6" t="n">
+        <v>13</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M5"/>
+  <autoFilter ref="A1:M6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4864,7 +4902,7 @@
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4909,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4958,7 +4996,7 @@
         <v>50</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5007,7 +5045,7 @@
         <v>26</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5060,7 +5098,7 @@
         <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5113,7 +5151,7 @@
         <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5162,7 +5200,7 @@
         <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5215,7 +5253,7 @@
         <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5264,7 +5302,7 @@
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5317,7 +5355,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5366,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5415,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5464,7 +5502,7 @@
         <v>50</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5513,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5562,7 +5600,7 @@
         <v>14</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5607,7 +5645,7 @@
         <v>32</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5656,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5705,7 +5743,7 @@
         <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5750,7 +5788,7 @@
         <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5796,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5835,7 +5873,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,32 +530,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33488</v>
+        <v>32500</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>50154</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>32,995 → 32,500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -570,21 +577,21 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32500</v>
+        <v>34392</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>50154</v>
+        <v>43909</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -593,7 +600,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>32,995 → 32,500</t>
+          <t>34,492 → 34,392</t>
         </is>
       </c>
     </row>
@@ -603,39 +610,48 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34392</v>
+        <v>34990</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>43909</v>
+        <v>60688</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>34,492 → 34,392</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -643,41 +659,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2023</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="n">
-        <v>34990</v>
+        <v>34992</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>60688</v>
+        <v>57600</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -686,50 +689,13 @@
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>57600</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>13</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4791,7 +4757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4879,18 +4845,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>35490</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>49731</v>
+        <v>33488</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -4899,19 +4862,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -4924,18 +4887,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>30995</v>
+        <v>35490</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>63212</v>
+        <v>49731</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -4944,19 +4907,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -4969,43 +4932,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>33495</v>
+        <v>30995</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>52500</v>
+        <v>63212</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5030,10 +4989,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5042,14 +5001,14 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5062,20 +5021,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5083,10 +5038,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>33995</v>
+        <v>32495</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>53180</v>
+        <v>69400</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5095,14 +5050,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5117,14 +5072,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>34,995 → 33,995</t>
+          <t>33,995 → 32,495</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5132,14 +5087,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>60487</v>
+        <v>53180</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5148,14 +5103,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5168,12 +5123,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5181,14 +5140,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>55829</v>
+        <v>60487</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5197,14 +5156,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5217,16 +5176,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5234,14 +5189,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34988</v>
+        <v>33995</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>61258</v>
+        <v>55829</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5250,14 +5205,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5270,12 +5225,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5283,14 +5242,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32893</v>
+        <v>34988</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>54959</v>
+        <v>61258</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5299,14 +5258,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5319,11 +5278,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983 → 32,893</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5340,10 +5295,10 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>35494</v>
+        <v>32893</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>47574</v>
+        <v>54959</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5352,14 +5307,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5372,12 +5327,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>34,994 → 34,983 → 32,893</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5385,30 +5344,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>35490</v>
+        <v>35494</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>49731</v>
+        <v>47574</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5426,38 +5385,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>35499</v>
+        <v>35490</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>48779</v>
+        <v>49731</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5475,7 +5434,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5483,35 +5442,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>32495</v>
+        <v>35499</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>67680</v>
+        <v>48779</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5524,43 +5483,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>59312</v>
+        <v>67680</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I15" t="n">
         <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5573,22 +5532,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>34895</v>
+        <v>34990</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>59350</v>
+        <v>59312</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5597,19 +5556,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5622,39 +5581,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>63289</v>
+        <v>59350</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5662,11 +5625,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5679,80 +5638,80 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5765,39 +5724,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>56361</v>
+        <v>44246</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5810,35 +5773,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" s="2" t="n">
+        <v>31998</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>61005</v>
+        <v>56361</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5856,13 +5818,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2024</v>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>61005</v>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
@@ -5873,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -5892,8 +5861,47 @@
       </c>
       <c r="M22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Toyotavictoriaville</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>21</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M22"/>
+  <autoFilter ref="A1:M23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5916,6 +5924,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4865,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>50</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>26</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>13</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>50</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>32</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>18</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5770,138 +5770,8 @@
       </c>
       <c r="M20" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" s="2" t="n">
-        <v>31998</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>56361</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>20</v>
-      </c>
-      <c r="I21" t="n">
-        <v>21</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>61005</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Toyotavictoriaville</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Toyotavictoriaville</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>21</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M23"/>
+  <autoFilter ref="A1:M20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5922,9 +5792,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>50</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>26</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>13</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>50</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>32</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>18</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>50</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>26</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>13</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>50</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>32</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>18</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -659,17 +659,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>34992</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>57600</v>
+        <v>63824</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -689,13 +689,50 @@
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>34992</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>18</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M5"/>
+  <autoFilter ref="A1:M6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4757,7 +4794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4845,36 +4882,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
-        <v>33488</v>
+        <v>34990</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>60688</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -4887,18 +4931,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>35490</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>49731</v>
+        <v>33488</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -4907,19 +4948,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -4932,18 +4973,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>30995</v>
+        <v>35490</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>63212</v>
+        <v>49731</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -4952,19 +4993,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -4977,43 +5018,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>33495</v>
+        <v>30995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>52500</v>
+        <v>63212</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5038,10 +5075,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5050,14 +5087,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5070,20 +5107,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5091,10 +5124,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>33995</v>
+        <v>32495</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>53180</v>
+        <v>69400</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5103,14 +5136,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5125,14 +5158,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>34,995 → 33,995</t>
+          <t>33,995 → 32,495</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5140,14 +5173,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60487</v>
+        <v>53180</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5156,14 +5189,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5176,12 +5209,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5189,14 +5226,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>55829</v>
+        <v>60487</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5205,14 +5242,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5225,16 +5262,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5242,14 +5275,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>34988</v>
+        <v>33995</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>61258</v>
+        <v>55829</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5258,14 +5291,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5278,12 +5311,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5291,14 +5328,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>32893</v>
+        <v>34988</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>54959</v>
+        <v>61258</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5307,14 +5344,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5327,11 +5364,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983 → 32,893</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5348,10 +5381,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>35494</v>
+        <v>32893</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>47574</v>
+        <v>54959</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5360,14 +5393,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5380,12 +5413,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>34,994 → 34,983 → 32,893</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5393,30 +5430,30 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>35490</v>
+        <v>35494</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>49731</v>
+        <v>47574</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5434,38 +5471,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>35499</v>
+        <v>35490</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>48779</v>
+        <v>49731</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5483,7 +5520,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5491,35 +5528,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>32495</v>
+        <v>35499</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>67680</v>
+        <v>48779</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5532,43 +5569,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>59312</v>
+        <v>67680</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I16" t="n">
         <v>15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5581,22 +5618,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>34895</v>
+        <v>34990</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>59350</v>
+        <v>59312</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -5605,19 +5642,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5630,39 +5667,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>63289</v>
+        <v>59350</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I18" t="n">
         <v>17</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5670,11 +5711,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5687,91 +5724,140 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
+          <t>Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>18</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>34992</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>44246</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>18</v>
       </c>
-      <c r="I20" t="n">
-        <v>19</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M20"/>
+  <autoFilter ref="A1:M21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5792,6 +5878,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -659,17 +659,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>34992</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>63824</v>
+        <v>57600</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -689,50 +689,13 @@
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>57600</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>18</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -744,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -796,12 +759,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No 2023–2024 sunroof lease-transfer matched this run.</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL S-AWC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>$558</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>48,800 kms</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Granby, 236 kms</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$592</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>103,000 kms</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Terrebonne, 167 kms</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV NOIR S-AWC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$679</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>48,000 kms</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Luskville, 21 kms</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$778</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30,000 kms</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sainte-Marthe-sur-le-Lac, 145 kms</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV SEL S-AWC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$877</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>23,000 kms</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mississauga, 374 kms</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G6"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4794,7 +4942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4882,43 +5030,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>34990</v>
+        <v>34992</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>60688</v>
+        <v>63824</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -4931,36 +5075,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>33488</v>
+        <v>34990</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>60688</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -4973,18 +5124,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>35490</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>49731</v>
+        <v>33488</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -4993,19 +5141,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5018,18 +5166,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>30995</v>
+        <v>35490</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>63212</v>
+        <v>49731</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5038,19 +5186,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5063,43 +5211,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>33495</v>
+        <v>30995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>52500</v>
+        <v>63212</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5124,10 +5268,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5136,14 +5280,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5156,20 +5300,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5177,10 +5317,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>33995</v>
+        <v>32495</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>53180</v>
+        <v>69400</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5189,14 +5329,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5211,14 +5351,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>34,995 → 33,995</t>
+          <t>33,995 → 32,495</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5226,14 +5366,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>60487</v>
+        <v>53180</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5242,14 +5382,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5262,12 +5402,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5275,14 +5419,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>55829</v>
+        <v>60487</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5291,14 +5435,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5311,16 +5455,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5328,14 +5468,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>34988</v>
+        <v>33995</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>61258</v>
+        <v>55829</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5344,14 +5484,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5364,12 +5504,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5377,14 +5521,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>32893</v>
+        <v>34988</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>54959</v>
+        <v>61258</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5393,14 +5537,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5413,11 +5557,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983 → 32,893</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5434,10 +5574,10 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>35494</v>
+        <v>32893</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>47574</v>
+        <v>54959</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5446,14 +5586,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5466,12 +5606,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>34,994 → 34,983 → 32,893</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5479,30 +5623,30 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>35490</v>
+        <v>35494</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>49731</v>
+        <v>47574</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5520,38 +5664,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>35499</v>
+        <v>35490</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>48779</v>
+        <v>49731</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5569,7 +5713,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5577,35 +5721,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>32495</v>
+        <v>35499</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>67680</v>
+        <v>48779</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5618,43 +5762,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>59312</v>
+        <v>67680</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5667,22 +5811,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>34895</v>
+        <v>34990</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>59350</v>
+        <v>59312</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -5691,19 +5835,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>17</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5716,39 +5860,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>63289</v>
+        <v>59350</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I19" t="n">
         <v>18</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5756,11 +5904,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5773,91 +5917,140 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>34895</v>
+        <v>34992</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>59350</v>
+        <v>63289</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>44246</v>
+        <v>59350</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>19</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>34992</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>44246</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>18</v>
       </c>
-      <c r="I21" t="n">
-        <v>20</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="I22" t="n">
+        <v>21</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M21"/>
+  <autoFilter ref="A1:M22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5879,6 +6072,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,39 +530,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32500</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>50154</v>
+        <v>31295</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 32,500</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -577,21 +570,21 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34392</v>
+        <v>31995</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>43909</v>
+        <v>50154</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -600,7 +593,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>34,492 → 34,392</t>
+          <t>32,995 → 32,500 → 31,995</t>
         </is>
       </c>
     </row>
@@ -610,48 +603,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34990</v>
+        <v>34392</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>60688</v>
+        <v>43909</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>34,492 → 34,392</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -659,43 +643,124 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2023</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>60688</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>34992</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>57600</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>19</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="K6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Hamel Honda</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M5"/>
+  <autoFilter ref="A1:M7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4942,7 +5007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5053,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5102,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5144,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5189,7 +5254,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5234,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5283,7 +5348,7 @@
         <v>50</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5332,7 +5397,7 @@
         <v>26</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5385,7 +5450,7 @@
         <v>21</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5438,7 +5503,7 @@
         <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5487,7 +5552,7 @@
         <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5540,7 +5605,7 @@
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5589,7 +5654,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5642,7 +5707,7 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5691,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5740,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5789,7 +5854,7 @@
         <v>50</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5838,7 +5903,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5887,7 +5952,7 @@
         <v>14</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5932,7 +5997,7 @@
         <v>32</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5981,7 +6046,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -6000,57 +6065,8 @@
       </c>
       <c r="M21" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>44246</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>18</v>
-      </c>
-      <c r="I22" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M22"/>
+  <autoFilter ref="A1:M21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6072,7 +6088,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>31995</v>
+        <v>31500</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>50154</v>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>32,995 → 32,500 → 31,995</t>
+          <t>32,995 → 32,500 → 31,995 → 31,500</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$558</t>
+          <t>$544</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>50</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>26</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>21</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>50</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>14</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>32</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -643,41 +643,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34990</v>
+        <v>34995</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>60688</v>
+        <v>51650</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Joliette Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -692,28 +679,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2023</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>34992</v>
+        <v>34990</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>57600</v>
+        <v>60688</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -733,27 +733,135 @@
       </c>
       <c r="C7" t="n">
         <v>2024</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>34992</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>62415</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>35295</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>60254</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Boucherville Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>34992</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>22</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Hamel Honda</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -761,6 +869,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5007,7 +5118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5118,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5167,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5209,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5254,7 +5365,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5299,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5348,7 +5459,7 @@
         <v>50</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5397,7 +5508,7 @@
         <v>26</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5450,7 +5561,7 @@
         <v>21</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5503,7 +5614,7 @@
         <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5552,7 +5663,7 @@
         <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5605,7 +5716,7 @@
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5654,7 +5765,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5707,7 +5818,7 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5756,7 +5867,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5805,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5854,7 +5965,7 @@
         <v>50</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5903,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5952,7 +6063,7 @@
         <v>14</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5971,102 +6082,8 @@
       </c>
       <c r="M19" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>63289</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>32</v>
-      </c>
-      <c r="I20" t="n">
-        <v>21</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>35,492 → 34,992</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" s="2" t="n">
-        <v>34895</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>59350</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>21</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M21"/>
+  <autoFilter ref="A1:M19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6086,8 +6103,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,32 +530,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31295</v>
+        <v>31500</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>50154</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>32,995 → 32,500 → 31,995 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -570,21 +577,21 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>31500</v>
+        <v>34392</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>50154</v>
+        <v>43909</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -593,7 +600,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>32,995 → 32,500 → 31,995 → 31,500</t>
+          <t>34,492 → 34,392</t>
         </is>
       </c>
     </row>
@@ -610,32 +617,28 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34392</v>
+        <v>34995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>43909</v>
+        <v>51650</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Blainville Mitsubishi, Joliette Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>34,492 → 34,392</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -643,28 +646,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34995</v>
+        <v>34990</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>51650</v>
+        <v>60688</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Joliette Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -679,41 +695,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34990</v>
+        <v>34992</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>60688</v>
+        <v>62415</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -735,21 +738,21 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34992</v>
+        <v>35295</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>62415</v>
+        <v>60254</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Boucherville Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -764,28 +767,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>35295</v>
+        <v>34992</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>60254</v>
+        <v>57600</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Boucherville Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -800,28 +803,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>57600</v>
+        <v>2024</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Hamel Honda</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -830,38 +827,8 @@
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hamel Honda</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -871,7 +838,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5206,39 +5172,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>63824</v>
+        <v>31295</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5251,34 +5214,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>34990</v>
+        <v>34992</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>60688</v>
+        <v>63824</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5300,36 +5259,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>33488</v>
+        <v>34990</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>60688</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5342,18 +5308,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>35490</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>49731</v>
+        <v>33488</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5362,19 +5325,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5387,18 +5350,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>30995</v>
+        <v>35490</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>63212</v>
+        <v>49731</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5407,19 +5370,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5432,43 +5395,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>33495</v>
+        <v>30995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>52500</v>
+        <v>63212</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5493,10 +5452,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5505,14 +5464,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5525,20 +5484,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5546,10 +5501,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>33995</v>
+        <v>32495</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>53180</v>
+        <v>69400</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5558,14 +5513,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5580,14 +5535,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>34,995 → 33,995</t>
+          <t>33,995 → 32,495</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5595,14 +5550,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>60487</v>
+        <v>53180</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5611,14 +5566,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5631,12 +5586,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5644,14 +5603,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>55829</v>
+        <v>60487</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5660,14 +5619,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5680,16 +5639,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5697,14 +5652,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>34988</v>
+        <v>33995</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>61258</v>
+        <v>55829</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5713,14 +5668,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5733,12 +5688,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5746,14 +5705,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>32893</v>
+        <v>34988</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>54959</v>
+        <v>61258</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5762,14 +5721,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5782,11 +5741,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983 → 32,893</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5803,10 +5758,10 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>35494</v>
+        <v>32893</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>47574</v>
+        <v>54959</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5815,14 +5770,14 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5835,12 +5790,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>34,994 → 34,983 → 32,893</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5848,30 +5807,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>35490</v>
+        <v>35494</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>49731</v>
+        <v>47574</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5889,38 +5848,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>35499</v>
+        <v>35490</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>48779</v>
+        <v>49731</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5938,7 +5897,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5946,35 +5905,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>32495</v>
+        <v>35499</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>67680</v>
+        <v>48779</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5987,43 +5946,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>59312</v>
+        <v>67680</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I18" t="n">
         <v>20</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -6036,22 +5995,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>34895</v>
+        <v>34990</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>59350</v>
+        <v>59312</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -6060,19 +6019,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>21</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34392</v>
+        <v>33992</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>43909</v>
+        <v>34250</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -591,18 +591,14 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>34,492 → 34,392</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -631,7 +627,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -680,7 +676,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -716,7 +712,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -752,7 +748,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -788,7 +784,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -818,7 +814,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1017,7 +1013,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$778</t>
+          <t>$775</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1027,7 +1023,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5172,36 +5168,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>31295</v>
+        <v>34392</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>43909</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5209,44 +5208,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>34,492 → 34,392</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>63824</v>
+        <v>31295</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5259,34 +5259,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>34990</v>
+        <v>34992</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>60688</v>
+        <v>63824</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5308,36 +5304,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="n">
-        <v>33488</v>
+        <v>34990</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>60688</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5350,18 +5353,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>35490</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>49731</v>
+        <v>33488</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5370,19 +5370,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5395,18 +5395,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>30995</v>
+        <v>35490</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>63212</v>
+        <v>49731</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5415,19 +5415,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5440,43 +5440,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>33495</v>
+        <v>30995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>52500</v>
+        <v>63212</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5501,10 +5497,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5513,14 +5509,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5533,20 +5529,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5554,10 +5546,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>33995</v>
+        <v>32495</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>53180</v>
+        <v>69400</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5566,14 +5558,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5588,14 +5580,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>34,995 → 33,995</t>
+          <t>33,995 → 32,495</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5603,14 +5595,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>60487</v>
+        <v>53180</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5619,14 +5611,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5639,12 +5631,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5652,14 +5648,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>55829</v>
+        <v>60487</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5668,14 +5664,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5688,16 +5684,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5705,14 +5697,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34988</v>
+        <v>33995</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>61258</v>
+        <v>55829</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5721,14 +5713,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5741,12 +5733,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5754,14 +5750,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>32893</v>
+        <v>34988</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>54959</v>
+        <v>61258</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5770,14 +5766,14 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5790,11 +5786,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983 → 32,893</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5811,10 +5803,10 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>35494</v>
+        <v>32893</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>47574</v>
+        <v>54959</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5823,14 +5815,14 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5843,12 +5835,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>34,994 → 34,983 → 32,893</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5856,30 +5852,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>35490</v>
+        <v>35494</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>49731</v>
+        <v>47574</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5897,38 +5893,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>35499</v>
+        <v>35490</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>48779</v>
+        <v>49731</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5946,7 +5942,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5954,35 +5950,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>32495</v>
+        <v>35499</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>67680</v>
+        <v>48779</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5995,43 +5991,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>59312</v>
+        <v>67680</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I19" t="n">
         <v>21</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5168,39 +5168,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
-        <v>34392</v>
+        <v>34990</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>43909</v>
+        <v>60688</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5208,45 +5212,44 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>34,492 → 34,392</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>31295</v>
+        <v>34392</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>43909</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5254,44 +5257,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>34,492 → 34,392</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>63824</v>
+        <v>31295</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5304,34 +5308,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>34990</v>
+        <v>34992</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>60688</v>
+        <v>63824</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>50</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>26</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5988,57 +5988,8 @@
       </c>
       <c r="M18" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>67680</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>50</v>
-      </c>
-      <c r="I19" t="n">
-        <v>21</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:M18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6057,7 +6008,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -5192,19 +5192,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5240,7 +5240,7 @@
         <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>50</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>26</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -971,27 +971,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV NOIR S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL S-AWC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$679</t>
+          <t>$715</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>48,000 kms</t>
+          <t>38,241 kms</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Luskville, 21 kms</t>
+          <t>Curran, 60 kms</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5195,7 +5195,7 @@
         <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>50</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>26</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$18</definedName>
   </definedNames>
@@ -537,32 +537,28 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31500</v>
+        <v>33992</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>50154</v>
+        <v>34250</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 32,500 → 31,995 → 31,500</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -577,21 +573,21 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33992</v>
+        <v>34995</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>34250</v>
+        <v>51650</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Blainville Mitsubishi, Joliette Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -606,28 +602,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34995</v>
+        <v>34990</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>51650</v>
+        <v>60688</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Joliette Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -642,41 +651,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34990</v>
+        <v>35490</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>60688</v>
+        <v>49731</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -712,7 +708,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -748,7 +744,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -784,7 +780,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -814,7 +810,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -845,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -971,27 +967,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV NOIR S-AWC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$715</t>
+          <t>$679</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>38,241 kms</t>
+          <t>48,000 kms</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Curran, 60 kms</t>
+          <t>Luskville, 21 kms</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1008,17 +1004,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL S-AWC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$775</t>
+          <t>$715</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30,000 kms</t>
+          <t>38,241 kms</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1028,7 +1024,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sainte-Marthe-sur-le-Lac, 145 kms</t>
+          <t>Curran, 60 kms</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1045,48 +1041,86 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2024 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$775</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>30,000 kms</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sainte-Marthe-sur-le-Lac, 145 kms</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>2024 Mitsubishi Outlander PHEV SEL S-AWC</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>$877</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>23,000 kms</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Mississauga, 374 kms</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5168,43 +5202,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>34990</v>
+        <v>31500</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>60688</v>
+        <v>50154</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5212,44 +5242,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>32,995 → 32,500 → 31,995 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>34392</v>
+        <v>34990</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>43909</v>
+        <v>60688</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5257,45 +5295,44 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>34,492 → 34,392</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>31295</v>
+        <v>34392</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>43909</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5303,44 +5340,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>34,492 → 34,392</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>63824</v>
+        <v>31295</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5353,36 +5391,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>33488</v>
+        <v>34992</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>63824</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5395,18 +5436,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>35490</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>49731</v>
+        <v>33488</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5415,19 +5453,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5463,7 +5501,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5512,7 +5550,7 @@
         <v>50</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5561,7 +5599,7 @@
         <v>26</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5614,7 +5652,7 @@
         <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5667,7 +5705,7 @@
         <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5716,7 +5754,7 @@
         <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5769,7 +5807,7 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5818,7 +5856,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5871,7 +5909,7 @@
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5920,7 +5958,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5969,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -759,28 +759,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>57600</v>
+        <v>2024</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Hamel Honda</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -789,38 +783,8 @@
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Hamel Honda</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -829,7 +793,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5114,7 +5077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5202,39 +5165,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>31500</v>
+        <v>34992</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>50154</v>
+        <v>57600</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5242,52 +5205,44 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 32,500 → 31,995 → 31,500</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>34990</v>
+        <v>31500</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>60688</v>
+        <v>50154</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5295,44 +5250,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>32,995 → 32,500 → 31,995 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>34392</v>
+        <v>34990</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>43909</v>
+        <v>60688</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5340,45 +5303,44 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>34,492 → 34,392</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>31295</v>
+        <v>34392</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>43909</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5386,44 +5348,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>34,492 → 34,392</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>63824</v>
+        <v>31295</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5436,36 +5399,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>33488</v>
+        <v>34992</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>63824</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5486,10 +5452,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>30995</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>63212</v>
+        <v>33488</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5498,19 +5461,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5523,43 +5486,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>33495</v>
+        <v>30995</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>52500</v>
+        <v>63212</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5584,10 +5543,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5596,14 +5555,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5616,20 +5575,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5637,10 +5592,10 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>33995</v>
+        <v>32495</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>53180</v>
+        <v>69400</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5649,14 +5604,14 @@
         </is>
       </c>
       <c r="H11" t="n">
+        <v>26</v>
+      </c>
+      <c r="I11" t="n">
         <v>21</v>
       </c>
-      <c r="I11" t="n">
-        <v>20</v>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5671,14 +5626,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>34,995 → 33,995</t>
+          <t>33,995 → 32,495</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5686,14 +5641,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>60487</v>
+        <v>53180</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5702,14 +5657,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5722,12 +5677,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5735,14 +5694,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>55829</v>
+        <v>60487</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5751,14 +5710,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5771,16 +5730,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5788,14 +5743,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34988</v>
+        <v>33995</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>61258</v>
+        <v>55829</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5804,14 +5759,14 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5824,12 +5779,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>34,995 → 33,995</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5837,14 +5796,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>32893</v>
+        <v>34988</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>54959</v>
+        <v>61258</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5853,14 +5812,14 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5873,11 +5832,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983 → 32,893</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5894,10 +5849,10 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>35494</v>
+        <v>32893</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>47574</v>
+        <v>54959</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5906,14 +5861,14 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5926,12 +5881,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>34,994 → 34,983 → 32,893</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5939,30 +5898,30 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>35490</v>
+        <v>35494</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>49731</v>
+        <v>47574</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5980,54 +5939,103 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>35499</v>
+        <v>35490</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>48779</v>
+        <v>49731</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>21</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>35499</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>48779</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Otogo.ca</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="n">
-        <v>20</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="I19" t="n">
+        <v>21</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
+  <autoFilter ref="A1:M19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6046,6 +6054,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,21 +573,21 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34995</v>
+        <v>34869</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>51650</v>
+        <v>50975</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Joliette Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Joliette Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -602,41 +602,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34990</v>
+        <v>34995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>60688</v>
+        <v>51650</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -651,28 +638,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35490</v>
+        <v>34990</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>49731</v>
+        <v>60688</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -694,21 +694,21 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34992</v>
+        <v>35490</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>62415</v>
+        <v>49731</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -730,21 +730,21 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35295</v>
+        <v>34992</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>60254</v>
+        <v>62415</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Boucherville Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -764,27 +764,63 @@
       </c>
       <c r="C8" t="n">
         <v>2024</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>35295</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>60254</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
+          <t>Boucherville Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Hamel Honda</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>9</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -793,6 +829,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5077,7 +5114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5188,7 +5225,7 @@
         <v>28</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5233,7 +5270,7 @@
         <v>21</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5286,7 +5323,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5331,7 +5368,7 @@
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5377,7 +5414,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5422,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5464,7 +5501,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5509,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5528,514 +5565,8 @@
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>33495</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>52500</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I10" t="n">
-        <v>21</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>32495</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>69400</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>26</v>
-      </c>
-      <c r="I11" t="n">
-        <v>21</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>33,995 → 32,495</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>53180</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>21</v>
-      </c>
-      <c r="I12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>60487</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>19</v>
-      </c>
-      <c r="I13" t="n">
-        <v>21</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>55829</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>13</v>
-      </c>
-      <c r="I14" t="n">
-        <v>21</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>34,995 → 33,995</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>34988</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>61258</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>9</v>
-      </c>
-      <c r="I15" t="n">
-        <v>21</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>32893</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>54959</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" t="n">
-        <v>21</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>34,994 → 34,983 → 32,893</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>35494</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>47574</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>21</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>35490</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>49731</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>21</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>35499</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>48779</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>21</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6045,16 +5576,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>28</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>21</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
